--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.01_b0.01_x0.30_Q4_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.01_b0.01_x0.30_Q4_LO.xlsx
@@ -455,10 +455,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.027552611194128</v>
+        <v>0.01624627135566048</v>
       </c>
       <c r="C2" t="n">
-        <v>0.027552611194128</v>
+        <v>0.01624627135566048</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.02703724197549435</v>
+        <v>0.01596253810782585</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02703724197549435</v>
+        <v>0.01596253810782585</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -483,10 +483,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.02710786787221389</v>
+        <v>0.01599551997210713</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02710786787221389</v>
+        <v>0.01599551997210713</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -497,10 +497,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.02711999936490093</v>
+        <v>0.01597938496737857</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02711999936490093</v>
+        <v>0.01597938496737857</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -511,10 +511,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.02685822948526004</v>
+        <v>0.01579414646328647</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02685822948526004</v>
+        <v>0.01579414646328647</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -525,10 +525,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.02665616981043147</v>
+        <v>0.01563947396254025</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02665616981043147</v>
+        <v>0.01563947396254025</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -539,10 +539,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.02628706393725765</v>
+        <v>0.0153861450554586</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02628706393725765</v>
+        <v>0.0153861450554586</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.02588603762595663</v>
+        <v>0.01511231815268333</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02588603762595663</v>
+        <v>0.01511231815268333</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -567,10 +567,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.02546145078836952</v>
+        <v>0.01482579047048281</v>
       </c>
       <c r="C10" t="n">
-        <v>0.02546145078836952</v>
+        <v>0.01482579047048281</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -581,10 +581,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.0250326828403966</v>
+        <v>0.01453991428889175</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0250326828403966</v>
+        <v>0.01453991428889175</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -595,10 +595,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.02461968624742322</v>
+        <v>0.01426733923428301</v>
       </c>
       <c r="C12" t="n">
-        <v>0.02461968624742322</v>
+        <v>0.01426733923428301</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -609,10 +609,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.02424243259942256</v>
+        <v>0.01402076690124343</v>
       </c>
       <c r="C13" t="n">
-        <v>0.02424243259942256</v>
+        <v>0.01402076690124343</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -623,10 +623,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.02391337134575696</v>
+        <v>0.01380783789715731</v>
       </c>
       <c r="C14" t="n">
-        <v>0.02391337134575696</v>
+        <v>0.01380783789715731</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -637,10 +637,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.02363767656298879</v>
+        <v>0.0136315581274673</v>
       </c>
       <c r="C15" t="n">
-        <v>0.02363767656298879</v>
+        <v>0.0136315581274673</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -651,10 +651,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.02341786641431846</v>
+        <v>0.01349320463786781</v>
       </c>
       <c r="C16" t="n">
-        <v>0.02341786641431846</v>
+        <v>0.01349320463786781</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -665,10 +665,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.02325778834632143</v>
+        <v>0.01339479610259011</v>
       </c>
       <c r="C17" t="n">
-        <v>0.02325778834632143</v>
+        <v>0.01339479610259011</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -679,10 +679,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.02316483470362217</v>
+        <v>0.01334045989661212</v>
       </c>
       <c r="C18" t="n">
-        <v>0.02316483470362217</v>
+        <v>0.01334045989661212</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.02314820723981737</v>
+        <v>0.01333536589960592</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02314820723981737</v>
+        <v>0.01333536589960592</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -707,10 +707,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.02321703101400207</v>
+        <v>0.01338462659678739</v>
       </c>
       <c r="C20" t="n">
-        <v>0.02321703101400207</v>
+        <v>0.01338462659678739</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -721,10 +721,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.02337876697675909</v>
+        <v>0.01349232533075579</v>
       </c>
       <c r="C21" t="n">
-        <v>0.02337876697675909</v>
+        <v>0.01349232533075579</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -735,10 +735,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.02363748005233123</v>
+        <v>0.01366041362155502</v>
       </c>
       <c r="C22" t="n">
-        <v>0.02363748005233123</v>
+        <v>0.01366041362155502</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -749,10 +749,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.02400085524010205</v>
+        <v>0.01389333155778027</v>
       </c>
       <c r="C23" t="n">
-        <v>0.02400085524010205</v>
+        <v>0.01389333155778027</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -763,10 +763,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.02441239443250617</v>
+        <v>0.01415739645045386</v>
       </c>
       <c r="C24" t="n">
-        <v>0.02441239443250617</v>
+        <v>0.01415739645045386</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -777,10 +777,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.02497655263660889</v>
+        <v>0.0145134866943529</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02497655263660889</v>
+        <v>0.0145134866943529</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -791,10 +791,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.02566038326898312</v>
+        <v>0.01494254685456897</v>
       </c>
       <c r="C26" t="n">
-        <v>0.02566038326898312</v>
+        <v>0.01494254685456897</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -805,10 +805,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.02647118749132978</v>
+        <v>0.01544834903603918</v>
       </c>
       <c r="C27" t="n">
-        <v>0.02647118749132978</v>
+        <v>0.01544834903603918</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -819,10 +819,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.02741432057721569</v>
+        <v>0.01603411945520229</v>
       </c>
       <c r="C28" t="n">
-        <v>0.02741432057721569</v>
+        <v>0.01603411945520229</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -833,10 +833,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.02849222119513055</v>
+        <v>0.01670098225169329</v>
       </c>
       <c r="C29" t="n">
-        <v>0.02849222119513055</v>
+        <v>0.01670098225169329</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -847,10 +847,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.02970636196024667</v>
+        <v>0.01744968184989594</v>
       </c>
       <c r="C30" t="n">
-        <v>0.02970636196024667</v>
+        <v>0.01744968184989594</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -861,10 +861,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.03105971192920311</v>
+        <v>0.01828183292223963</v>
       </c>
       <c r="C31" t="n">
-        <v>0.03105971192920311</v>
+        <v>0.01828183292223963</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
